--- a/Project 3 - Gantt Chart.xlsx
+++ b/Project 3 - Gantt Chart.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7cbf3353e9af97e5/Desktop/SP2026/CODES/PROJECT 3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7cbf3353e9af97e5/Desktop/SP2026/CODES/PROJECT 3/Submissions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="623" documentId="8_{2D0532B1-89FC-4489-A866-D32F74691416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{107C0D6F-D607-49F2-B8C6-400805D186F7}"/>
+  <xr:revisionPtr revIDLastSave="698" documentId="8_{2D0532B1-89FC-4489-A866-D32F74691416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02407EE2-3E6A-42BC-A9B2-9A114CC96335}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1105,25 +1105,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1141,20 +1144,17 @@
     <xf numFmtId="166" fontId="11" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -2743,84 +2743,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>204108</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>40821</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>326572</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>163286</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB841C6C-4D99-6F99-E121-049170BBF70D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9198429" y="10218964"/>
-          <a:ext cx="6490607" cy="1646465"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="2400" kern="1200"/>
-            <a:t>DATES DUE ARE UNKNOWN, WILL ADJUST ONCE DATES ARE GIVEN</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="2400" kern="1200"/>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="2400" kern="1200"/>
-            <a:t>(this is a draft - will be updated for final)</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>53</xdr:col>
       <xdr:colOff>20113</xdr:colOff>
       <xdr:row>49</xdr:row>
@@ -2889,245 +2811,6 @@
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
             <a:t>G</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>20040</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>120237</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>142505</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>242702</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="TextBox 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9765E76C-0740-453A-82FB-150F0D41257A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9337222" y="16018328"/>
-          <a:ext cx="6357010" cy="1646465"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="2400" kern="1200"/>
-            <a:t>DATES</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="2400" kern="1200" baseline="0"/>
-            <a:t> DUE ARE UNKNOWN, WILL ADJUST ONCE DATES ARE GIVEN</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="2400" kern="1200" baseline="0"/>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="2400" kern="1200" baseline="0"/>
-            <a:t>(this is a draft - will be updated for final)</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="2400" kern="1200"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>273876</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>367887</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>49977</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>109352</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="TextBox 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D81BC6E6-DC67-478F-A96A-34AB9106E840}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9244694" y="19313978"/>
-          <a:ext cx="6357010" cy="1646465"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="2400" kern="1200"/>
-            <a:t>DATES DUE ARE UNKNOWN, WILL ADJUST ONCE DATES ARE GIVEN</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="2400" kern="1200"/>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="2400" kern="1200"/>
-            <a:t>(this is a draft - will be updated for final)</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>111579</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>302078</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>234044</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>43543</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="TextBox 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3890878F-55B4-49AB-B2B3-A906C262C63B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15120258" y="5527221"/>
-          <a:ext cx="6490607" cy="1646465"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="2400" kern="1200"/>
-            <a:t>DATES DUE ARE UNKNOWN, WILL ADJUST ONCE DATES ARE GIVEN</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-US" sz="2400" kern="1200"/>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-US" sz="2400" kern="1200"/>
-            <a:t>(this is a draft - will be updated for final)</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3370,92 +3053,92 @@
       <c r="E1" s="9"/>
       <c r="F1" s="10"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="100"/>
-      <c r="O1" s="100"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
       <c r="P1" s="11"/>
-      <c r="Q1" s="98">
+      <c r="Q1" s="99">
         <v>46079</v>
       </c>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AZ1" s="103" t="s">
+      <c r="R1" s="98"/>
+      <c r="S1" s="98"/>
+      <c r="T1" s="98"/>
+      <c r="U1" s="98"/>
+      <c r="V1" s="98"/>
+      <c r="W1" s="98"/>
+      <c r="X1" s="98"/>
+      <c r="Y1" s="98"/>
+      <c r="Z1" s="98"/>
+      <c r="AZ1" s="89" t="s">
         <v>35</v>
       </c>
-      <c r="BA1" s="104"/>
-      <c r="BB1" s="104"/>
-      <c r="BC1" s="104"/>
-      <c r="BD1" s="104"/>
-      <c r="BE1" s="104"/>
-      <c r="BF1" s="104"/>
-      <c r="BG1" s="105"/>
+      <c r="BA1" s="90"/>
+      <c r="BB1" s="90"/>
+      <c r="BC1" s="90"/>
+      <c r="BD1" s="90"/>
+      <c r="BE1" s="90"/>
+      <c r="BF1" s="90"/>
+      <c r="BG1" s="91"/>
       <c r="BH1" s="70"/>
     </row>
     <row r="2" spans="1:60" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="101" t="s">
+      <c r="B2" s="102" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="I2" s="99" t="s">
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="I2" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="100"/>
-      <c r="O2" s="100"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="101"/>
       <c r="P2" s="11"/>
-      <c r="Q2" s="96">
+      <c r="Q2" s="97">
         <v>1</v>
       </c>
-      <c r="R2" s="97"/>
-      <c r="S2" s="97"/>
-      <c r="T2" s="97"/>
-      <c r="U2" s="97"/>
-      <c r="V2" s="97"/>
-      <c r="W2" s="97"/>
-      <c r="X2" s="97"/>
-      <c r="Y2" s="97"/>
-      <c r="Z2" s="97"/>
+      <c r="R2" s="98"/>
+      <c r="S2" s="98"/>
+      <c r="T2" s="98"/>
+      <c r="U2" s="98"/>
+      <c r="V2" s="98"/>
+      <c r="W2" s="98"/>
+      <c r="X2" s="98"/>
+      <c r="Y2" s="98"/>
+      <c r="Z2" s="98"/>
       <c r="AZ2" s="70"/>
-      <c r="BB2" s="106" t="s">
+      <c r="BB2" s="92" t="s">
         <v>30</v>
       </c>
-      <c r="BC2" s="106"/>
-      <c r="BD2" s="106"/>
-      <c r="BE2" s="106"/>
+      <c r="BC2" s="92"/>
+      <c r="BD2" s="92"/>
+      <c r="BE2" s="92"/>
       <c r="BF2" s="70"/>
       <c r="BH2" s="70"/>
     </row>
     <row r="3" spans="1:60" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="B3" s="101"/>
-      <c r="C3" s="101"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="101"/>
-      <c r="F3" s="101"/>
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
       <c r="AZ3" s="76"/>
-      <c r="BB3" s="106"/>
-      <c r="BC3" s="106"/>
-      <c r="BD3" s="106"/>
-      <c r="BE3" s="106"/>
+      <c r="BB3" s="92"/>
+      <c r="BC3" s="92"/>
+      <c r="BD3" s="92"/>
+      <c r="BE3" s="92"/>
       <c r="BF3" s="71"/>
       <c r="BG3" s="77"/>
       <c r="BH3" s="71"/>
@@ -3464,83 +3147,83 @@
       <c r="A4" s="5"/>
       <c r="B4" s="13"/>
       <c r="E4" s="14"/>
-      <c r="I4" s="102">
+      <c r="I4" s="103">
         <f>I5</f>
         <v>46076</v>
       </c>
-      <c r="J4" s="95"/>
-      <c r="K4" s="95"/>
-      <c r="L4" s="95"/>
-      <c r="M4" s="95"/>
-      <c r="N4" s="95"/>
-      <c r="O4" s="95"/>
-      <c r="P4" s="95">
+      <c r="J4" s="94"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="94"/>
+      <c r="M4" s="94"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="94"/>
+      <c r="P4" s="94">
         <f>P5</f>
         <v>46083</v>
       </c>
-      <c r="Q4" s="95"/>
-      <c r="R4" s="95"/>
-      <c r="S4" s="95"/>
-      <c r="T4" s="95"/>
-      <c r="U4" s="95"/>
-      <c r="V4" s="95"/>
-      <c r="W4" s="95">
+      <c r="Q4" s="94"/>
+      <c r="R4" s="94"/>
+      <c r="S4" s="94"/>
+      <c r="T4" s="94"/>
+      <c r="U4" s="94"/>
+      <c r="V4" s="94"/>
+      <c r="W4" s="94">
         <f>W5</f>
         <v>46090</v>
       </c>
-      <c r="X4" s="95"/>
-      <c r="Y4" s="95"/>
-      <c r="Z4" s="95"/>
-      <c r="AA4" s="95"/>
-      <c r="AB4" s="95"/>
-      <c r="AC4" s="95"/>
-      <c r="AD4" s="95">
+      <c r="X4" s="94"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="94"/>
+      <c r="AA4" s="94"/>
+      <c r="AB4" s="94"/>
+      <c r="AC4" s="94"/>
+      <c r="AD4" s="94">
         <f t="shared" ref="AD4" si="0">AD5</f>
         <v>46097</v>
       </c>
-      <c r="AE4" s="95"/>
-      <c r="AF4" s="95"/>
-      <c r="AG4" s="95"/>
-      <c r="AH4" s="95"/>
-      <c r="AI4" s="95"/>
-      <c r="AJ4" s="95"/>
-      <c r="AK4" s="95">
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94">
         <f t="shared" ref="AK4" si="1">AK5</f>
         <v>46104</v>
       </c>
-      <c r="AL4" s="95"/>
-      <c r="AM4" s="95"/>
-      <c r="AN4" s="95"/>
-      <c r="AO4" s="95"/>
-      <c r="AP4" s="95"/>
-      <c r="AQ4" s="95"/>
-      <c r="AR4" s="95">
+      <c r="AL4" s="94"/>
+      <c r="AM4" s="94"/>
+      <c r="AN4" s="94"/>
+      <c r="AO4" s="94"/>
+      <c r="AP4" s="94"/>
+      <c r="AQ4" s="94"/>
+      <c r="AR4" s="94">
         <v>46101</v>
       </c>
-      <c r="AS4" s="95"/>
-      <c r="AT4" s="95"/>
-      <c r="AU4" s="95"/>
-      <c r="AV4" s="95"/>
-      <c r="AW4" s="95"/>
-      <c r="AX4" s="95"/>
+      <c r="AS4" s="94"/>
+      <c r="AT4" s="94"/>
+      <c r="AU4" s="94"/>
+      <c r="AV4" s="94"/>
+      <c r="AW4" s="94"/>
+      <c r="AX4" s="94"/>
       <c r="AZ4" s="71"/>
       <c r="BH4" s="71"/>
     </row>
     <row r="5" spans="1:60" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="89"/>
-      <c r="B5" s="90" t="s">
+      <c r="A5" s="104"/>
+      <c r="B5" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="92" t="s">
+      <c r="C5" s="107" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="94" t="s">
+      <c r="D5" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="94" t="s">
+      <c r="E5" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="94" t="s">
+      <c r="F5" s="95" t="s">
         <v>6</v>
       </c>
       <c r="I5" s="15">
@@ -3715,12 +3398,12 @@
       <c r="BH5" s="71"/>
     </row>
     <row r="6" spans="1:60" s="12" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="89"/>
-      <c r="B6" s="91"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="93"/>
+      <c r="A6" s="104"/>
+      <c r="B6" s="106"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="96"/>
+      <c r="E6" s="96"/>
+      <c r="F6" s="96"/>
       <c r="I6" s="18" t="str">
         <f t="shared" ref="I6:AX6" si="24">LEFT(TEXT(I5,"ddd"),1)</f>
         <v>M</v>
@@ -4009,22 +3692,22 @@
       <c r="AV8" s="28"/>
       <c r="AW8" s="28"/>
       <c r="AX8" s="28"/>
-      <c r="AZ8" s="107" t="s">
+      <c r="AZ8" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="BA8" s="107"/>
-      <c r="BB8" s="107" t="s">
+      <c r="BA8" s="93"/>
+      <c r="BB8" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="BC8" s="107"/>
-      <c r="BD8" s="107" t="s">
+      <c r="BC8" s="93"/>
+      <c r="BD8" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="BE8" s="107"/>
-      <c r="BF8" s="107" t="s">
+      <c r="BE8" s="93"/>
+      <c r="BF8" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="BG8" s="107"/>
+      <c r="BG8" s="93"/>
       <c r="BH8" s="72"/>
     </row>
     <row r="9" spans="1:60" s="29" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -4036,7 +3719,7 @@
         <v>37</v>
       </c>
       <c r="D9" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="33">
         <v>46079</v>
@@ -4106,7 +3789,7 @@
         <v>37</v>
       </c>
       <c r="D10" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="38">
         <v>46079</v>
@@ -4176,7 +3859,7 @@
         <v>37</v>
       </c>
       <c r="D11" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="38">
         <v>46101</v>
@@ -4246,7 +3929,7 @@
         <v>37</v>
       </c>
       <c r="D12" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="38">
         <v>46105</v>
@@ -4316,7 +3999,7 @@
         <v>37</v>
       </c>
       <c r="D13" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="38">
         <v>46108</v>
@@ -4412,7 +4095,7 @@
         <v>37</v>
       </c>
       <c r="D15" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="48">
         <v>46077</v>
@@ -4482,7 +4165,7 @@
         <v>37</v>
       </c>
       <c r="D16" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="48">
         <v>46078</v>
@@ -4552,7 +4235,7 @@
         <v>37</v>
       </c>
       <c r="D17" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="48">
         <v>46081</v>
@@ -4619,7 +4302,7 @@
         <v>37</v>
       </c>
       <c r="D18" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="48">
         <v>46082</v>
@@ -4689,7 +4372,7 @@
         <v>37</v>
       </c>
       <c r="D19" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="48">
         <v>46086</v>
@@ -4759,7 +4442,7 @@
         <v>37</v>
       </c>
       <c r="D20" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="48">
         <v>46087</v>
@@ -5312,14 +4995,18 @@
         <v>37</v>
       </c>
       <c r="D28" s="67">
-        <v>0</v>
-      </c>
-      <c r="E28" s="68"/>
-      <c r="F28" s="68"/>
+        <v>1</v>
+      </c>
+      <c r="E28" s="68">
+        <v>46086</v>
+      </c>
+      <c r="F28" s="68">
+        <v>46091</v>
+      </c>
       <c r="G28" s="6"/>
-      <c r="H28" s="3" t="str">
+      <c r="H28" s="3">
         <f t="shared" si="25"/>
-        <v/>
+        <v>6</v>
       </c>
       <c r="I28" s="34"/>
       <c r="J28" s="34"/>
@@ -5378,14 +5065,18 @@
         <v>37</v>
       </c>
       <c r="D29" s="67">
-        <v>0</v>
-      </c>
-      <c r="E29" s="68"/>
-      <c r="F29" s="68"/>
+        <v>1</v>
+      </c>
+      <c r="E29" s="68">
+        <v>46086</v>
+      </c>
+      <c r="F29" s="68">
+        <v>46091</v>
+      </c>
       <c r="G29" s="6"/>
-      <c r="H29" s="3" t="str">
+      <c r="H29" s="3">
         <f t="shared" si="25"/>
-        <v/>
+        <v>6</v>
       </c>
       <c r="I29" s="34"/>
       <c r="J29" s="34"/>
@@ -5444,14 +5135,18 @@
         <v>37</v>
       </c>
       <c r="D30" s="67">
-        <v>0</v>
-      </c>
-      <c r="E30" s="68"/>
-      <c r="F30" s="68"/>
+        <v>1</v>
+      </c>
+      <c r="E30" s="68">
+        <v>46091</v>
+      </c>
+      <c r="F30" s="68">
+        <v>46093</v>
+      </c>
       <c r="G30" s="6"/>
-      <c r="H30" s="3" t="str">
+      <c r="H30" s="3">
         <f t="shared" si="25"/>
-        <v/>
+        <v>3</v>
       </c>
       <c r="I30" s="34"/>
       <c r="J30" s="34"/>
@@ -5510,14 +5205,18 @@
         <v>37</v>
       </c>
       <c r="D31" s="67">
-        <v>0</v>
-      </c>
-      <c r="E31" s="68"/>
-      <c r="F31" s="68"/>
+        <v>1</v>
+      </c>
+      <c r="E31" s="68">
+        <v>46092</v>
+      </c>
+      <c r="F31" s="68">
+        <v>46094</v>
+      </c>
       <c r="G31" s="6"/>
-      <c r="H31" s="3" t="str">
+      <c r="H31" s="3">
         <f t="shared" si="25"/>
-        <v/>
+        <v>3</v>
       </c>
       <c r="I31" s="34"/>
       <c r="J31" s="34"/>
@@ -5576,10 +5275,14 @@
         <v>37</v>
       </c>
       <c r="D32" s="67">
-        <v>0</v>
-      </c>
-      <c r="E32" s="68"/>
-      <c r="F32" s="68"/>
+        <v>1</v>
+      </c>
+      <c r="E32" s="68">
+        <v>46092</v>
+      </c>
+      <c r="F32" s="68">
+        <v>46094</v>
+      </c>
       <c r="G32" s="6"/>
       <c r="H32" s="3"/>
       <c r="I32" s="34"/>
@@ -5639,14 +5342,18 @@
         <v>37</v>
       </c>
       <c r="D33" s="67">
-        <v>0</v>
-      </c>
-      <c r="E33" s="68"/>
-      <c r="F33" s="68"/>
+        <v>1</v>
+      </c>
+      <c r="E33" s="68">
+        <v>46094</v>
+      </c>
+      <c r="F33" s="68">
+        <v>46096</v>
+      </c>
       <c r="G33" s="6"/>
-      <c r="H33" s="3" t="str">
+      <c r="H33" s="3">
         <f t="shared" si="25"/>
-        <v/>
+        <v>3</v>
       </c>
       <c r="I33" s="34"/>
       <c r="J33" s="34"/>
@@ -5775,7 +5482,7 @@
         <v>37</v>
       </c>
       <c r="D35" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="33">
         <v>46080</v>
@@ -5844,7 +5551,7 @@
         <v>37</v>
       </c>
       <c r="D36" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="38">
         <v>46087</v>
@@ -5910,7 +5617,7 @@
         <v>37</v>
       </c>
       <c r="D37" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="38">
         <v>46094</v>
@@ -5976,7 +5683,7 @@
         <v>37</v>
       </c>
       <c r="D38" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="38">
         <v>46108</v>
@@ -6042,7 +5749,7 @@
         <v>37</v>
       </c>
       <c r="D39" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="38">
         <v>46109</v>
@@ -6108,7 +5815,7 @@
         <v>37</v>
       </c>
       <c r="D40" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" s="38">
         <v>46112</v>
@@ -6244,14 +5951,18 @@
         <v>37</v>
       </c>
       <c r="D42" s="47">
-        <v>0</v>
-      </c>
-      <c r="E42" s="48"/>
-      <c r="F42" s="48"/>
+        <v>1</v>
+      </c>
+      <c r="E42" s="48">
+        <v>46109</v>
+      </c>
+      <c r="F42" s="48">
+        <v>46111</v>
+      </c>
       <c r="G42" s="6"/>
-      <c r="H42" s="3" t="str">
+      <c r="H42" s="3">
         <f t="shared" si="26"/>
-        <v/>
+        <v>3</v>
       </c>
       <c r="I42" s="34"/>
       <c r="J42" s="34"/>
@@ -6310,10 +6021,14 @@
         <v>37</v>
       </c>
       <c r="D43" s="47">
-        <v>0</v>
-      </c>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
+        <v>1</v>
+      </c>
+      <c r="E43" s="48">
+        <v>46109</v>
+      </c>
+      <c r="F43" s="48">
+        <v>46111</v>
+      </c>
       <c r="G43" s="6"/>
       <c r="H43" s="3"/>
       <c r="I43" s="34"/>
@@ -6372,10 +6087,14 @@
         <v>37</v>
       </c>
       <c r="D44" s="47">
-        <v>0</v>
-      </c>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
+        <v>1</v>
+      </c>
+      <c r="E44" s="48">
+        <v>46109</v>
+      </c>
+      <c r="F44" s="48">
+        <v>46111</v>
+      </c>
       <c r="G44" s="6"/>
       <c r="H44" s="3"/>
       <c r="I44" s="34"/>
@@ -6434,10 +6153,14 @@
         <v>37</v>
       </c>
       <c r="D45" s="47">
-        <v>0</v>
-      </c>
-      <c r="E45" s="48"/>
-      <c r="F45" s="48"/>
+        <v>1</v>
+      </c>
+      <c r="E45" s="48">
+        <v>46109</v>
+      </c>
+      <c r="F45" s="48">
+        <v>46111</v>
+      </c>
       <c r="G45" s="6"/>
       <c r="H45" s="3"/>
       <c r="I45" s="34"/>
@@ -6496,10 +6219,14 @@
         <v>37</v>
       </c>
       <c r="D46" s="47">
-        <v>0</v>
-      </c>
-      <c r="E46" s="48"/>
-      <c r="F46" s="48"/>
+        <v>1</v>
+      </c>
+      <c r="E46" s="48">
+        <v>46109</v>
+      </c>
+      <c r="F46" s="48">
+        <v>46111</v>
+      </c>
       <c r="G46" s="6"/>
       <c r="H46" s="3"/>
       <c r="I46" s="34"/>
@@ -6558,7 +6285,7 @@
         <v>37</v>
       </c>
       <c r="D47" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="48">
         <v>46110</v>
@@ -6624,7 +6351,7 @@
         <v>37</v>
       </c>
       <c r="D48" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" s="48">
         <v>46112</v>
@@ -6691,7 +6418,9 @@
         <v>13</v>
       </c>
       <c r="C49" s="50"/>
-      <c r="D49" s="51"/>
+      <c r="D49" s="51">
+        <v>0.01</v>
+      </c>
       <c r="E49" s="52"/>
       <c r="F49" s="53"/>
       <c r="G49" s="6"/>
@@ -6761,12 +6490,16 @@
       <c r="D50" s="57">
         <v>0</v>
       </c>
-      <c r="E50" s="58"/>
-      <c r="F50" s="58"/>
+      <c r="E50" s="58">
+        <v>46109</v>
+      </c>
+      <c r="F50" s="58">
+        <v>46111</v>
+      </c>
       <c r="G50" s="6"/>
-      <c r="H50" s="3" t="str">
+      <c r="H50" s="3">
         <f t="shared" si="27"/>
-        <v/>
+        <v>3</v>
       </c>
       <c r="I50" s="34"/>
       <c r="J50" s="34"/>
@@ -6827,8 +6560,12 @@
       <c r="D51" s="57">
         <v>0</v>
       </c>
-      <c r="E51" s="58"/>
-      <c r="F51" s="58"/>
+      <c r="E51" s="58">
+        <v>46109</v>
+      </c>
+      <c r="F51" s="58">
+        <v>46111</v>
+      </c>
       <c r="G51" s="6"/>
       <c r="H51" s="3"/>
       <c r="I51" s="34"/>
@@ -6889,8 +6626,12 @@
       <c r="D52" s="57">
         <v>0</v>
       </c>
-      <c r="E52" s="58"/>
-      <c r="F52" s="58"/>
+      <c r="E52" s="58">
+        <v>46109</v>
+      </c>
+      <c r="F52" s="58">
+        <v>46111</v>
+      </c>
       <c r="G52" s="6"/>
       <c r="H52" s="3"/>
       <c r="I52" s="34"/>
@@ -6951,8 +6692,12 @@
       <c r="D53" s="57">
         <v>0</v>
       </c>
-      <c r="E53" s="58"/>
-      <c r="F53" s="58"/>
+      <c r="E53" s="58">
+        <v>46109</v>
+      </c>
+      <c r="F53" s="58">
+        <v>46111</v>
+      </c>
       <c r="G53" s="6"/>
       <c r="H53" s="3"/>
       <c r="I53" s="34"/>
@@ -7017,7 +6762,7 @@
         <v>46108</v>
       </c>
       <c r="F54" s="58">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="3"/>
@@ -7273,12 +7018,11 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="AZ1:BG1"/>
-    <mergeCell ref="BB2:BE3"/>
-    <mergeCell ref="BD8:BE8"/>
-    <mergeCell ref="BB8:BC8"/>
-    <mergeCell ref="AZ8:BA8"/>
-    <mergeCell ref="BF8:BG8"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="AR4:AX4"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="Q2:Z2"/>
@@ -7291,11 +7035,12 @@
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
     <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="AZ1:BG1"/>
+    <mergeCell ref="BB2:BE3"/>
+    <mergeCell ref="BD8:BE8"/>
+    <mergeCell ref="BB8:BC8"/>
+    <mergeCell ref="AZ8:BA8"/>
+    <mergeCell ref="BF8:BG8"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:D57">
     <cfRule type="dataBar" priority="47">
@@ -7406,6 +7151,26 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7717,26 +7482,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
   <ds:schemaRefs>
@@ -7746,6 +7491,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A09426A3-87E9-4865-8A6C-3456B026AE03}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7766,18 +7523,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>